--- a/input/reg_health_mental.xlsx
+++ b/input/reg_health_mental.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF27609-5500-4E8F-A059-053D7C9F8DB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC491EDB-607A-4A8A-BFE1-DBE864B901E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="14400" windowHeight="15600" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="60">
   <si>
     <t>Date modified</t>
   </si>
@@ -202,6 +202,24 @@
   </si>
   <si>
     <t>Dcpst_PreviouslyPartnered_L1</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_ZERO</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_TEN</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_TWENTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_THIRTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC_Lhw_FORTY</t>
+  </si>
+  <si>
+    <t>D_Econ_benefits_UC</t>
   </si>
 </sst>
 </file>
@@ -3885,13 +3903,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35101A52-F636-4EA1-B514-C92ACE822888}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -3928,8 +3946,26 @@
       <c r="L1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3966,8 +4002,26 @@
       <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4004,8 +4058,26 @@
       <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4042,8 +4114,26 @@
       <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4080,8 +4170,26 @@
       <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4118,8 +4226,26 @@
       <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4156,8 +4282,26 @@
       <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -4194,8 +4338,26 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4232,80 +4394,470 @@
       <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B16" s="4">
         <v>0.7547488</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
         <v>2.0778007724100004E-3</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B17" s="4">
         <v>6.9100000000000003E-3</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
         <v>2.0550899556099999E-3</v>
       </c>
     </row>
@@ -4317,13 +4869,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F83C27E0-FA2B-440E-9BE2-866FFC98D161}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:R17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -4360,8 +4912,26 @@
       <c r="L1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" t="s">
+        <v>54</v>
+      </c>
+      <c r="N1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O1" t="s">
+        <v>56</v>
+      </c>
+      <c r="P1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>58</v>
+      </c>
+      <c r="R1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4398,8 +4968,26 @@
       <c r="L2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4436,8 +5024,26 @@
       <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4474,8 +5080,26 @@
       <c r="L4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4512,8 +5136,26 @@
       <c r="L5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4550,8 +5192,26 @@
       <c r="L6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4588,8 +5248,26 @@
       <c r="L7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
@@ -4626,8 +5304,26 @@
       <c r="L8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>42</v>
       </c>
@@ -4664,80 +5360,470 @@
       <c r="L9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="4">
+      <c r="B16" s="4">
         <v>0.7547488</v>
       </c>
-      <c r="C10">
-        <v>0</v>
-      </c>
-      <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>0</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" s="6">
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16">
+        <v>0</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>0</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="6">
         <v>2.0778007724100004E-3</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="R16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="4">
+      <c r="B17" s="4">
         <v>6.9100000000000003E-3</v>
       </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11" s="6">
+      <c r="C17">
+        <v>0</v>
+      </c>
+      <c r="D17">
+        <v>0</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+      <c r="F17">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>0</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17" s="6">
         <v>2.0550899556099999E-3</v>
       </c>
     </row>
@@ -7613,14 +8699,14 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90524CD9-FC25-43D3-A993-DE235AB6CC61}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="8" customWidth="1"/>
     <col min="2" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>2</v>
       </c>
@@ -7651,8 +8737,26 @@
       <c r="J1" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -7683,8 +8787,26 @@
       <c r="J2" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -7715,8 +8837,26 @@
       <c r="J3" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
@@ -7747,8 +8887,26 @@
       <c r="J4" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -7779,8 +8937,26 @@
       <c r="J5" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -7811,8 +8987,26 @@
       <c r="J6" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -7843,8 +9037,26 @@
       <c r="J7" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -7875,8 +9087,26 @@
       <c r="J8" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>42</v>
       </c>
@@ -7906,6 +9136,324 @@
       </c>
       <c r="J9" s="8">
         <v>4.7043339317226502E-3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -7916,14 +9464,14 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AC91F47-2228-4CD9-A074-8E6E16867A5F}">
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:P15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.7109375" style="8" customWidth="1"/>
     <col min="2" max="16384" width="11.42578125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>2</v>
       </c>
@@ -7954,8 +9502,26 @@
       <c r="J1" s="8" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K1" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" t="s">
+        <v>58</v>
+      </c>
+      <c r="P1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>9</v>
       </c>
@@ -7986,8 +9552,26 @@
       <c r="J2" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>10</v>
       </c>
@@ -8018,8 +9602,26 @@
       <c r="J3" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>11</v>
       </c>
@@ -8050,8 +9652,26 @@
       <c r="J4" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>12</v>
       </c>
@@ -8082,8 +9702,26 @@
       <c r="J5" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>13</v>
       </c>
@@ -8114,8 +9752,26 @@
       <c r="J6" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>14</v>
       </c>
@@ -8146,8 +9802,26 @@
       <c r="J7" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>41</v>
       </c>
@@ -8178,8 +9852,26 @@
       <c r="J8" s="8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>42</v>
       </c>
@@ -8209,6 +9901,324 @@
       </c>
       <c r="J9" s="8">
         <v>4.4853158471408801E-3</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B12">
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>58</v>
+      </c>
+      <c r="B14">
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_health_mental.xlsx
+++ b/input/reg_health_mental.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC491EDB-607A-4A8A-BFE1-DBE864B901E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46220635-BFE1-4E74-AC54-FCD8B2863DA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4698,7 +4698,7 @@
         <v>59</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -4740,7 +4740,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.3408999999999999E-2</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>59</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>0.312</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -5706,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>2.3408999999999999E-2</v>
       </c>
       <c r="Q15">
         <v>0</v>

--- a/input/reg_health_mental.xlsx
+++ b/input/reg_health_mental.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\andy_local\SimPaths project files\SimPaths\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DF70282-FA2F-4B0E-8AE0-ED4D25C04B44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{991DC341-07EE-EB40-B59A-A24404BECEB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="7" r:id="rId1"/>
-    <sheet name="UK_HM1_L" sheetId="8" r:id="rId2"/>
-    <sheet name="UK_HM2_Females_L" sheetId="9" r:id="rId3"/>
-    <sheet name="UK_HM2_Males_L" sheetId="10" r:id="rId4"/>
-    <sheet name="UK_HM1_C" sheetId="11" r:id="rId5"/>
-    <sheet name="UK_HM2_Females_C" sheetId="12" r:id="rId6"/>
-    <sheet name="UK_HM2_Males_C" sheetId="13" r:id="rId7"/>
+    <sheet name="HM1_L" sheetId="8" r:id="rId2"/>
+    <sheet name="HM2_Females_L" sheetId="9" r:id="rId3"/>
+    <sheet name="HM2_Males_L" sheetId="10" r:id="rId4"/>
+    <sheet name="HM1_C" sheetId="11" r:id="rId5"/>
+    <sheet name="HM2_Females_C" sheetId="12" r:id="rId6"/>
+    <sheet name="HM2_Males_C" sheetId="13" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -208,6 +208,7 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -578,9 +579,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6DDC330-9BDF-4603-A68D-0C2E2D7CEC2E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -590,12 +591,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2243EDC-2254-468B-8D3E-B3F418BFBCA7}">
   <dimension ref="A1:AG32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -696,7 +697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -797,7 +798,7 @@
         <v>-2.6043987477358924E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -898,7 +899,7 @@
         <v>-1.4034720409174949E-3</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -999,7 +1000,7 @@
         <v>-3.2140193580960057E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -1100,7 +1101,7 @@
         <v>-9.4634212899048396E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -1201,7 +1202,7 @@
         <v>-1.585621456900126E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -1302,7 +1303,7 @@
         <v>-1.6500440563494781E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -1403,7 +1404,7 @@
         <v>-1.7236132545426746E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -1504,7 +1505,7 @@
         <v>-1.5488975991081897E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -1605,7 +1606,7 @@
         <v>-1.5739638898629703E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -1706,7 +1707,7 @@
         <v>-1.5647880757328227E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -1807,7 +1808,7 @@
         <v>-1.6038454062750739E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -1908,7 +1909,7 @@
         <v>-1.6620642965992647E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -2009,7 +2010,7 @@
         <v>-1.7397406038015559E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>-1.6170414830774722E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -2211,7 +2212,7 @@
         <v>-1.6548466967051876E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -2312,7 +2313,7 @@
         <v>-1.0133868569238576E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -2413,7 +2414,7 @@
         <v>-9.5287804851535535E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -2514,7 +2515,7 @@
         <v>-8.9630371734848084E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -2615,7 +2616,7 @@
         <v>-1.0080958152018805E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -2716,7 +2717,7 @@
         <v>-8.3425277593053744E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -2817,7 +2818,7 @@
         <v>-1.5749495161941271E-4</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -2918,7 +2919,7 @@
         <v>-2.3608457114923117E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -3019,7 +3020,7 @@
         <v>1.8909574094302535E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -3120,7 +3121,7 @@
         <v>-7.4778121837295848E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -3221,7 +3222,7 @@
         <v>-1.1370672435674473E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -3322,7 +3323,7 @@
         <v>-9.7220212048864177E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -3423,7 +3424,7 @@
         <v>-1.5158460921093368E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -3524,7 +3525,7 @@
         <v>-1.0294149806037516E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -3625,7 +3626,7 @@
         <v>-5.2866686697276236E-4</v>
       </c>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -3726,7 +3727,7 @@
         <v>-7.6683574797224409E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>31</v>
       </c>
@@ -3835,12 +3836,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19ED6DFE-C7BD-4842-98F1-709F3188C44C}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3881,7 +3882,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -3922,7 +3923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -3963,7 +3964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -4004,7 +4005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -4045,7 +4046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -4086,7 +4087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -4127,7 +4128,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -4168,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -4209,7 +4210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -4250,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -4291,7 +4292,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -4340,12 +4341,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A93277EA-A3FA-4F87-A840-095FA0D38FE2}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4386,7 +4387,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -4427,7 +4428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -4468,7 +4469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -4509,7 +4510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -4550,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -4591,7 +4592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -4632,7 +4633,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -4673,7 +4674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -4714,7 +4715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -4755,7 +4756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -4796,7 +4797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -4845,12 +4846,12 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A965793-981C-401A-9DD5-9CB2E2F7D36F}">
   <dimension ref="A1:AR43"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -4984,7 +4985,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -5118,7 +5119,7 @@
         <v>-5.7194239990527906E-5</v>
       </c>
     </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -5252,7 +5253,7 @@
         <v>2.74655309073602E-4</v>
       </c>
     </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>-1.4739039039187883E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
@@ -5520,7 +5521,7 @@
         <v>2.5806290807364473E-5</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
@@ -5654,7 +5655,7 @@
         <v>5.1098715600890357E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -5788,7 +5789,7 @@
         <v>5.2579987040840244E-4</v>
       </c>
     </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -5922,7 +5923,7 @@
         <v>5.3697990874964588E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
@@ -6056,7 +6057,7 @@
         <v>4.8821649387903747E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
@@ -6190,7 +6191,7 @@
         <v>4.7971561042579522E-4</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
@@ -6324,7 +6325,7 @@
         <v>4.6033420221542687E-4</v>
       </c>
     </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
@@ -6458,7 +6459,7 @@
         <v>5.1606525261374287E-4</v>
       </c>
     </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
@@ -6592,7 +6593,7 @@
         <v>4.748228261702164E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
@@ -6726,7 +6727,7 @@
         <v>5.2098405592732435E-4</v>
       </c>
     </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
@@ -6860,7 +6861,7 @@
         <v>5.0735325029304822E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
@@ -6994,7 +6995,7 @@
         <v>5.1161502807439306E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
@@ -7128,7 +7129,7 @@
         <v>3.2431565147847722E-4</v>
       </c>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>3.6363457087671314E-4</v>
       </c>
     </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
@@ -7396,7 +7397,7 @@
         <v>3.0239505947473374E-4</v>
       </c>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
@@ -7530,7 +7531,7 @@
         <v>1.9172946612048514E-4</v>
       </c>
     </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
@@ -7664,7 +7665,7 @@
         <v>2.3188883180813623E-4</v>
       </c>
     </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
@@ -7798,7 +7799,7 @@
         <v>3.3012179816069297E-5</v>
       </c>
     </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
@@ -7932,7 +7933,7 @@
         <v>4.6451538361423785E-4</v>
       </c>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
@@ -8066,7 +8067,7 @@
         <v>-5.1293621571113368E-6</v>
       </c>
     </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
@@ -8200,7 +8201,7 @@
         <v>1.2972458229062021E-4</v>
       </c>
     </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
@@ -8334,7 +8335,7 @@
         <v>1.8967538718291172E-4</v>
       </c>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
@@ -8468,7 +8469,7 @@
         <v>3.1064957197797526E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -8602,7 +8603,7 @@
         <v>3.3238846214717912E-4</v>
       </c>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
@@ -8736,7 +8737,7 @@
         <v>2.9640453500198922E-4</v>
       </c>
     </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>29</v>
       </c>
@@ -8870,7 +8871,7 @@
         <v>9.0816458021191415E-5</v>
       </c>
     </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>30</v>
       </c>
@@ -9004,7 +9005,7 @@
         <v>4.6638675610461744E-5</v>
       </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>44</v>
       </c>
@@ -9138,7 +9139,7 @@
         <v>1.2728476562700227E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>45</v>
       </c>
@@ -9272,7 +9273,7 @@
         <v>1.2725530309268079E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>46</v>
       </c>
@@ -9406,7 +9407,7 @@
         <v>1.271239443470765E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>47</v>
       </c>
@@ -9540,7 +9541,7 @@
         <v>1.2726647804897885E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>48</v>
       </c>
@@ -9674,7 +9675,7 @@
         <v>1.274673505099134E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>49</v>
       </c>
@@ -9808,7 +9809,7 @@
         <v>1.276500189712308E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>50</v>
       </c>
@@ -9942,7 +9943,7 @@
         <v>1.278951753831082E-2</v>
       </c>
     </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>51</v>
       </c>
@@ -10076,7 +10077,7 @@
         <v>1.2819324543001767E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>52</v>
       </c>
@@ -10210,7 +10211,7 @@
         <v>1.2846550536580376E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>53</v>
       </c>
@@ -10344,7 +10345,7 @@
         <v>1.2914644033624073E-2</v>
       </c>
     </row>
-    <row r="42" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>54</v>
       </c>
@@ -10478,7 +10479,7 @@
         <v>1.2982358021083849E-2</v>
       </c>
     </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>55</v>
       </c>
@@ -10620,12 +10621,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE1170-73A3-4064-A59A-E2A113C17F8D}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10666,7 +10667,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -10707,7 +10708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -10748,7 +10749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -10789,7 +10790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -10830,7 +10831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -10871,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -10912,7 +10913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -10953,7 +10954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -10994,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -11035,7 +11036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -11076,7 +11077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
@@ -11125,12 +11126,12 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C98EB7F6-69F5-4701-8609-C8F5A0E52064}">
   <dimension ref="A1:M12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="16384" width="9.1640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -11171,7 +11172,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>33</v>
       </c>
@@ -11212,7 +11213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>34</v>
       </c>
@@ -11253,7 +11254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>35</v>
       </c>
@@ -11294,7 +11295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>36</v>
       </c>
@@ -11335,7 +11336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>37</v>
       </c>
@@ -11376,7 +11377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>38</v>
       </c>
@@ -11417,7 +11418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>39</v>
       </c>
@@ -11458,7 +11459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>40</v>
       </c>
@@ -11499,7 +11500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>41</v>
       </c>
@@ -11540,7 +11541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
@@ -11581,7 +11582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>43</v>
       </c>
